--- a/final_result/stock/quality_momentum_rs_lv_n500.xlsx
+++ b/final_result/stock/quality_momentum_rs_lv_n500.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221.85</v>
+        <v>3400.2</v>
       </c>
       <c r="F2" t="n">
-        <v>221.85</v>
+        <v>3400.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1253.48</v>
+        <v>809.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="I2" t="n">
-        <v>41.21</v>
+        <v>19.05</v>
       </c>
       <c r="J2" t="n">
-        <v>64.67</v>
+        <v>43.3</v>
       </c>
       <c r="K2" t="n">
-        <v>36.67</v>
+        <v>80.25</v>
       </c>
       <c r="L2" t="n">
-        <v>94.61</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="3">
@@ -530,42 +530,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7230</v>
+        <v>2743.5</v>
       </c>
       <c r="F3" t="n">
-        <v>7230</v>
+        <v>2743.5</v>
       </c>
       <c r="G3" t="n">
-        <v>324.97</v>
+        <v>139.71</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="I3" t="n">
-        <v>19.74</v>
+        <v>17.22</v>
       </c>
       <c r="J3" t="n">
-        <v>43.94</v>
+        <v>33.83</v>
       </c>
       <c r="K3" t="n">
-        <v>40.27</v>
+        <v>55.49</v>
       </c>
       <c r="L3" t="n">
-        <v>28.89</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -584,32 +584,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5266.4</v>
+        <v>32515</v>
       </c>
       <c r="F4" t="n">
-        <v>5266.4</v>
+        <v>32515</v>
       </c>
       <c r="G4" t="n">
-        <v>319.36</v>
+        <v>421.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="I4" t="n">
-        <v>14.26</v>
+        <v>12.41</v>
       </c>
       <c r="J4" t="n">
-        <v>31.47</v>
+        <v>43.04</v>
       </c>
       <c r="K4" t="n">
-        <v>23.44</v>
+        <v>47.67</v>
       </c>
       <c r="L4" t="n">
-        <v>49.65</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="5">
@@ -618,42 +618,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>299.55</v>
+        <v>1321</v>
       </c>
       <c r="F5" t="n">
-        <v>299.55</v>
+        <v>1321</v>
       </c>
       <c r="G5" t="n">
-        <v>534.21</v>
+        <v>139.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.46</v>
+        <v>2.04</v>
       </c>
       <c r="I5" t="n">
-        <v>3.99</v>
+        <v>22.64</v>
       </c>
       <c r="J5" t="n">
-        <v>14.16</v>
+        <v>57.48</v>
       </c>
       <c r="K5" t="n">
-        <v>25.37</v>
+        <v>44.56</v>
       </c>
       <c r="L5" t="n">
-        <v>31.41</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="6">
@@ -662,42 +662,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>813.35</v>
+        <v>744</v>
       </c>
       <c r="F6" t="n">
-        <v>813.35</v>
+        <v>744</v>
       </c>
       <c r="G6" t="n">
-        <v>233.47</v>
+        <v>116.38</v>
       </c>
       <c r="H6" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="I6" t="n">
-        <v>19.56</v>
+        <v>13.47</v>
       </c>
       <c r="J6" t="n">
-        <v>40.07</v>
+        <v>28.53</v>
       </c>
       <c r="K6" t="n">
-        <v>12.82</v>
+        <v>38.95</v>
       </c>
       <c r="L6" t="n">
-        <v>23.03</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="7">
@@ -706,42 +706,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>399.15</v>
+        <v>4026.7</v>
       </c>
       <c r="F7" t="n">
-        <v>399.15</v>
+        <v>4026.7</v>
       </c>
       <c r="G7" t="n">
-        <v>452.55</v>
+        <v>1309.42</v>
       </c>
       <c r="H7" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>9.460000000000001</v>
+        <v>14.02</v>
       </c>
       <c r="J7" t="n">
-        <v>15.55</v>
+        <v>26.74</v>
       </c>
       <c r="K7" t="n">
-        <v>19.59</v>
+        <v>45.09</v>
       </c>
       <c r="L7" t="n">
-        <v>22.95</v>
+        <v>68.28</v>
       </c>
     </row>
     <row r="8">
@@ -750,42 +750,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>481.45</v>
+        <v>1326.1</v>
       </c>
       <c r="F8" t="n">
-        <v>481.45</v>
+        <v>1326.1</v>
       </c>
       <c r="G8" t="n">
-        <v>578.89</v>
+        <v>271.09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.13</v>
+        <v>16.88</v>
       </c>
       <c r="J8" t="n">
-        <v>9.859999999999999</v>
+        <v>30.95</v>
       </c>
       <c r="K8" t="n">
-        <v>28.01</v>
+        <v>34.18</v>
       </c>
       <c r="L8" t="n">
-        <v>35.32</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="9">
@@ -794,42 +794,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1657.3</v>
+        <v>1202.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1657.3</v>
+        <v>1202.6</v>
       </c>
       <c r="G9" t="n">
-        <v>559.02</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="I9" t="n">
-        <v>19.63</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>19.93</v>
+        <v>41.59</v>
       </c>
       <c r="K9" t="n">
-        <v>16.88</v>
+        <v>46.75</v>
       </c>
       <c r="L9" t="n">
-        <v>18.69</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="10">
@@ -838,42 +838,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1458.6</v>
+        <v>1519.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1458.6</v>
+        <v>1519.1</v>
       </c>
       <c r="G10" t="n">
-        <v>338.54</v>
+        <v>175.16</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>23.53</v>
+        <v>9.6</v>
       </c>
       <c r="J10" t="n">
-        <v>13.47</v>
+        <v>32.49</v>
       </c>
       <c r="K10" t="n">
-        <v>15.38</v>
+        <v>30.04</v>
       </c>
       <c r="L10" t="n">
-        <v>28.94</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="11">
@@ -882,42 +882,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>448.4</v>
+        <v>607.75</v>
       </c>
       <c r="F11" t="n">
-        <v>448.4</v>
+        <v>607.75</v>
       </c>
       <c r="G11" t="n">
-        <v>420.88</v>
+        <v>49.74</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="I11" t="n">
-        <v>12.75</v>
+        <v>8.99</v>
       </c>
       <c r="J11" t="n">
-        <v>19.15</v>
+        <v>26.93</v>
       </c>
       <c r="K11" t="n">
-        <v>16.85</v>
+        <v>35.86</v>
       </c>
       <c r="L11" t="n">
-        <v>12.07</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="12">
@@ -926,42 +926,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4385.2</v>
+        <v>1745.7</v>
       </c>
       <c r="F12" t="n">
-        <v>4385.2</v>
+        <v>1745.7</v>
       </c>
       <c r="G12" t="n">
-        <v>528.37</v>
+        <v>124.58</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>7.86</v>
+        <v>7.54</v>
       </c>
       <c r="J12" t="n">
-        <v>10.31</v>
+        <v>42.79</v>
       </c>
       <c r="K12" t="n">
-        <v>17.98</v>
+        <v>32.56</v>
       </c>
       <c r="L12" t="n">
-        <v>26.64</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="13">
@@ -970,42 +970,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>318.35</v>
+        <v>1063.65</v>
       </c>
       <c r="F13" t="n">
-        <v>318.35</v>
+        <v>1063.65</v>
       </c>
       <c r="G13" t="n">
-        <v>358.7</v>
+        <v>67.63</v>
       </c>
       <c r="H13" t="n">
-        <v>1.24</v>
+        <v>2.33</v>
       </c>
       <c r="I13" t="n">
-        <v>8.73</v>
+        <v>13.09</v>
       </c>
       <c r="J13" t="n">
-        <v>23.91</v>
+        <v>29.94</v>
       </c>
       <c r="K13" t="n">
-        <v>13.56</v>
+        <v>34.91</v>
       </c>
       <c r="L13" t="n">
-        <v>12.55</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="14">
@@ -1014,42 +1014,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>444.55</v>
+        <v>4333.7</v>
       </c>
       <c r="F14" t="n">
-        <v>444.55</v>
+        <v>4333.7</v>
       </c>
       <c r="G14" t="n">
-        <v>406</v>
+        <v>291.15</v>
       </c>
       <c r="H14" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="I14" t="n">
-        <v>16.93</v>
+        <v>4.72</v>
       </c>
       <c r="J14" t="n">
-        <v>25.21</v>
+        <v>18.03</v>
       </c>
       <c r="K14" t="n">
-        <v>11.51</v>
+        <v>38.56</v>
       </c>
       <c r="L14" t="n">
-        <v>12.44</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="15">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3278.8</v>
+        <v>781.35</v>
       </c>
       <c r="F15" t="n">
-        <v>3278.8</v>
+        <v>781.35</v>
       </c>
       <c r="G15" t="n">
-        <v>145.51</v>
+        <v>174.57</v>
       </c>
       <c r="H15" t="n">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>27.8</v>
+        <v>15.04</v>
       </c>
       <c r="J15" t="n">
-        <v>50.37</v>
+        <v>17.15</v>
       </c>
       <c r="K15" t="n">
-        <v>4.53</v>
+        <v>37.46</v>
       </c>
       <c r="L15" t="n">
-        <v>7.94</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="16">
@@ -1102,42 +1102,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Next50</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1038</v>
+        <v>5402</v>
       </c>
       <c r="F16" t="n">
-        <v>1038</v>
+        <v>5402</v>
       </c>
       <c r="G16" t="n">
-        <v>605.05</v>
+        <v>228.52</v>
       </c>
       <c r="H16" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="I16" t="n">
-        <v>14.75</v>
+        <v>5.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.99</v>
+        <v>23.81</v>
       </c>
       <c r="K16" t="n">
-        <v>22.27</v>
+        <v>23.46</v>
       </c>
       <c r="L16" t="n">
-        <v>50.78</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="17">
@@ -1146,42 +1146,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>211.36</v>
+        <v>1928</v>
       </c>
       <c r="F17" t="n">
-        <v>211.36</v>
+        <v>1928</v>
       </c>
       <c r="G17" t="n">
-        <v>547.89</v>
+        <v>281.27</v>
       </c>
       <c r="H17" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="I17" t="n">
-        <v>8.609999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="J17" t="n">
-        <v>9.029999999999999</v>
+        <v>15.14</v>
       </c>
       <c r="K17" t="n">
-        <v>16.25</v>
+        <v>37.67</v>
       </c>
       <c r="L17" t="n">
-        <v>30.93</v>
+        <v>66.17</v>
       </c>
     </row>
     <row r="18">
@@ -1190,42 +1190,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1223.1</v>
+        <v>1094.05</v>
       </c>
       <c r="F18" t="n">
-        <v>1223.1</v>
+        <v>1094.05</v>
       </c>
       <c r="G18" t="n">
-        <v>182.96</v>
+        <v>20.27</v>
       </c>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="I18" t="n">
-        <v>7.53</v>
+        <v>16.38</v>
       </c>
       <c r="J18" t="n">
-        <v>9.26</v>
+        <v>29.53</v>
       </c>
       <c r="K18" t="n">
-        <v>13.94</v>
+        <v>22.93</v>
       </c>
       <c r="L18" t="n">
-        <v>22.53</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="19">
@@ -1234,42 +1234,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4185.1</v>
+        <v>355.35</v>
       </c>
       <c r="F19" t="n">
-        <v>4185.1</v>
+        <v>355.35</v>
       </c>
       <c r="G19" t="n">
-        <v>157.1</v>
+        <v>19.81</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.91</v>
       </c>
       <c r="J19" t="n">
-        <v>6.44</v>
+        <v>21.72</v>
       </c>
       <c r="K19" t="n">
-        <v>17.82</v>
+        <v>29.29</v>
       </c>
       <c r="L19" t="n">
-        <v>16.93</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="20">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1288,32 +1288,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1808.3</v>
+        <v>1290.8</v>
       </c>
       <c r="F20" t="n">
-        <v>1808.3</v>
+        <v>1290.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1026.62</v>
+        <v>44.45</v>
       </c>
       <c r="H20" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="I20" t="n">
-        <v>4.62</v>
+        <v>26.23</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>27.24</v>
       </c>
       <c r="K20" t="n">
-        <v>7.89</v>
+        <v>26.79</v>
       </c>
       <c r="L20" t="n">
-        <v>7.12</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="21">
@@ -1322,42 +1322,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9994</v>
+        <v>1062.4</v>
       </c>
       <c r="F21" t="n">
-        <v>9994</v>
+        <v>1062.4</v>
       </c>
       <c r="G21" t="n">
-        <v>376.39</v>
+        <v>229.95</v>
       </c>
       <c r="H21" t="n">
-        <v>1.69</v>
+        <v>2.28</v>
       </c>
       <c r="I21" t="n">
-        <v>12.35</v>
+        <v>15.02</v>
       </c>
       <c r="J21" t="n">
-        <v>5.94</v>
+        <v>24.27</v>
       </c>
       <c r="K21" t="n">
-        <v>10.34</v>
+        <v>18.17</v>
       </c>
       <c r="L21" t="n">
-        <v>23.76</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="22">
@@ -1366,42 +1366,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>15439</v>
+        <v>1045.1</v>
       </c>
       <c r="F22" t="n">
-        <v>15439</v>
+        <v>1045.1</v>
       </c>
       <c r="G22" t="n">
-        <v>212.54</v>
+        <v>60.22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>20.55</v>
+        <v>-2.17</v>
       </c>
       <c r="J22" t="n">
-        <v>10.94</v>
+        <v>21.4</v>
       </c>
       <c r="K22" t="n">
-        <v>10.13</v>
+        <v>41.79</v>
       </c>
       <c r="L22" t="n">
-        <v>4.66</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="23">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1424,28 +1424,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1068.45</v>
+        <v>1080.4</v>
       </c>
       <c r="F23" t="n">
-        <v>1068.45</v>
+        <v>1080.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1804.23</v>
+        <v>438.49</v>
       </c>
       <c r="H23" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="I23" t="n">
-        <v>4.98</v>
+        <v>3.98</v>
       </c>
       <c r="J23" t="n">
-        <v>0.47</v>
+        <v>11.85</v>
       </c>
       <c r="K23" t="n">
-        <v>14.86</v>
+        <v>36</v>
       </c>
       <c r="L23" t="n">
-        <v>32.47</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="24">
@@ -1454,42 +1454,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Midcap</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1264.5</v>
+        <v>9173.5</v>
       </c>
       <c r="F24" t="n">
-        <v>1264.5</v>
+        <v>9173.5</v>
       </c>
       <c r="G24" t="n">
-        <v>267.06</v>
+        <v>426.67</v>
       </c>
       <c r="H24" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="I24" t="n">
-        <v>10.88</v>
+        <v>12.11</v>
       </c>
       <c r="J24" t="n">
-        <v>3.76</v>
+        <v>17.4</v>
       </c>
       <c r="K24" t="n">
-        <v>6.78</v>
+        <v>19.45</v>
       </c>
       <c r="L24" t="n">
-        <v>23.14</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="25">
@@ -1498,42 +1498,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7636.5</v>
+        <v>1507.8</v>
       </c>
       <c r="F25" t="n">
-        <v>7636.5</v>
+        <v>1507.8</v>
       </c>
       <c r="G25" t="n">
-        <v>269.76</v>
+        <v>146.06</v>
       </c>
       <c r="H25" t="n">
-        <v>1.05</v>
+        <v>2.35</v>
       </c>
       <c r="I25" t="n">
-        <v>4.53</v>
+        <v>5.86</v>
       </c>
       <c r="J25" t="n">
-        <v>11.18</v>
+        <v>11.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.97</v>
+        <v>31.88</v>
       </c>
       <c r="L25" t="n">
-        <v>2.52</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="26">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1556,28 +1556,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4014</v>
+        <v>1817.3</v>
       </c>
       <c r="F26" t="n">
-        <v>4014</v>
+        <v>1817.3</v>
       </c>
       <c r="G26" t="n">
-        <v>1261.45</v>
+        <v>581.29</v>
       </c>
       <c r="H26" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="I26" t="n">
-        <v>11.27</v>
+        <v>15.5</v>
       </c>
       <c r="J26" t="n">
-        <v>5.8</v>
+        <v>16.99</v>
       </c>
       <c r="K26" t="n">
-        <v>1.04</v>
+        <v>20.6</v>
       </c>
       <c r="L26" t="n">
-        <v>16.59</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="27">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1596,32 +1596,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6502.5</v>
+        <v>760</v>
       </c>
       <c r="F27" t="n">
-        <v>6502.5</v>
+        <v>760</v>
       </c>
       <c r="G27" t="n">
-        <v>193.46</v>
+        <v>97.23</v>
       </c>
       <c r="H27" t="n">
-        <v>1.15</v>
+        <v>1.81</v>
       </c>
       <c r="I27" t="n">
-        <v>9.34</v>
+        <v>10.44</v>
       </c>
       <c r="J27" t="n">
-        <v>7.37</v>
+        <v>27.14</v>
       </c>
       <c r="K27" t="n">
-        <v>0.19</v>
+        <v>12.03</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.31</v>
+        <v>31.73</v>
       </c>
     </row>
     <row r="28">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1640,32 +1640,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1268.3</v>
+        <v>3573</v>
       </c>
       <c r="F28" t="n">
-        <v>1268.3</v>
+        <v>3573</v>
       </c>
       <c r="G28" t="n">
-        <v>952.1900000000001</v>
+        <v>78.81</v>
       </c>
       <c r="H28" t="n">
-        <v>2.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>-1.46</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.9</v>
+        <v>20.81</v>
       </c>
       <c r="K28" t="n">
-        <v>1.77</v>
+        <v>14.7</v>
       </c>
       <c r="L28" t="n">
-        <v>16.78</v>
+        <v>36.35</v>
       </c>
     </row>
     <row r="29">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1684,32 +1684,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>431.3</v>
+        <v>1029.5</v>
       </c>
       <c r="F29" t="n">
-        <v>431.3</v>
+        <v>1029.5</v>
       </c>
       <c r="G29" t="n">
-        <v>577.14</v>
+        <v>189.92</v>
       </c>
       <c r="H29" t="n">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="I29" t="n">
-        <v>3.01</v>
+        <v>5.26</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.38</v>
+        <v>15.62</v>
       </c>
       <c r="K29" t="n">
-        <v>4.74</v>
+        <v>15.3</v>
       </c>
       <c r="L29" t="n">
-        <v>9.85</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="30">
@@ -1718,42 +1718,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NiftyNext50</t>
+          <t>Nifty50</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>134.65</v>
+        <v>300.9</v>
       </c>
       <c r="F30" t="n">
-        <v>134.65</v>
+        <v>300.9</v>
       </c>
       <c r="G30" t="n">
-        <v>279.19</v>
+        <v>508.87</v>
       </c>
       <c r="H30" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="I30" t="n">
-        <v>5.77</v>
+        <v>5.93</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.64</v>
+        <v>12.16</v>
       </c>
       <c r="K30" t="n">
-        <v>3.59</v>
+        <v>24.3</v>
       </c>
       <c r="L30" t="n">
-        <v>21.57</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="31">
@@ -1762,42 +1762,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Smallcap</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1144.6</v>
+        <v>1081.7</v>
       </c>
       <c r="F31" t="n">
-        <v>1144.6</v>
+        <v>1081.7</v>
       </c>
       <c r="G31" t="n">
-        <v>180.48</v>
+        <v>90.95</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="I31" t="n">
-        <v>11.8</v>
+        <v>11.39</v>
       </c>
       <c r="J31" t="n">
-        <v>1.13</v>
+        <v>14.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.08</v>
+        <v>21.49</v>
       </c>
       <c r="L31" t="n">
-        <v>8.550000000000001</v>
+        <v>30.66</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -1864,182 +1864,130 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nifty50</t>
+          <t>Next50</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NiftyNext50</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>45</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pct</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pct</t>
-        </is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fast Moving Consumer Goods</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Automobile and Auto Components</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2054,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,7 +2025,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2037,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2061,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2085,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>biweekly: computed baseline as-of 2026-04-17 (n_ranked=34; archive cutoff 2026-04-17 00:00:00)</t>
+          <t>biweekly: computed baseline as-of 2026-05-01 (n_ranked=154; archive cutoff 2026-05-01 00:00:00)</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2097,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-12T20:46:46</t>
+          <t>2026-05-15T13:13:04</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2109,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2121,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-12T20:46:47</t>
+          <t>2026-05-15T13:13:06</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2168,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1) Current session — top 20 portfolio (this run, session 2026-05-01)</t>
+          <t>1) Current session — top 20 portfolio (this run, session 2026-05-15)</t>
         </is>
       </c>
     </row>
@@ -2244,265 +2192,261 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>221.85</v>
+        <v>3400.2</v>
       </c>
       <c r="C19" t="n">
-        <v>11.76</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7230</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.27</v>
-      </c>
+        <v>2743.5</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5266.4</v>
+        <v>32515</v>
       </c>
       <c r="C21" t="n">
-        <v>2.44</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>299.55</v>
+        <v>1321</v>
       </c>
       <c r="C22" t="n">
-        <v>5.46</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>813.35</v>
+        <v>744</v>
       </c>
       <c r="C23" t="n">
-        <v>4.98</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>399.15</v>
+        <v>4026.7</v>
       </c>
       <c r="C24" t="n">
-        <v>1.41</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>481.45</v>
+        <v>1326.1</v>
       </c>
       <c r="C25" t="n">
-        <v>9.73</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1657.3</v>
+        <v>1202.6</v>
       </c>
       <c r="C26" t="n">
-        <v>5.33</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1458.6</v>
+        <v>1519.1</v>
       </c>
       <c r="C27" t="n">
-        <v>13.46</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>448.4</v>
+        <v>607.75</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.54</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4385.2</v>
+        <v>1745.7</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.11</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>318.35</v>
+        <v>1063.65</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>444.55</v>
+        <v>4333.7</v>
       </c>
       <c r="C31" t="n">
-        <v>3.96</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3278.8</v>
+        <v>781.35</v>
       </c>
       <c r="C32" t="n">
-        <v>8.58</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1038</v>
+        <v>5402</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>211.36</v>
+        <v>1928</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.36</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1223.1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-3.69</v>
-      </c>
+        <v>1094.05</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4185.1</v>
+        <v>355.35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.13</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1808.3</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
+        <v>1290.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14.27</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9994</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2.26</v>
-      </c>
+        <v>1062.4</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2) Previous baseline — IN/OUT symbols: Adj close at baseline session 2026-04-17 vs current session 2026-05-01</t>
+          <t>2) Previous baseline — IN/OUT symbols: Adj close at baseline session 2026-05-01 vs current session 2026-05-15</t>
         </is>
       </c>
     </row>
@@ -2531,321 +2475,321 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>198.5</v>
+        <v>33550</v>
       </c>
       <c r="C43" t="n">
-        <v>221.85</v>
+        <v>32515</v>
       </c>
       <c r="D43" t="n">
-        <v>11.76</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7000.87</v>
+        <v>4466.2</v>
       </c>
       <c r="C44" t="n">
-        <v>7230</v>
+        <v>4333.7</v>
       </c>
       <c r="D44" t="n">
-        <v>3.27</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5140.9</v>
+        <v>1266.75</v>
       </c>
       <c r="C45" t="n">
-        <v>5266.4</v>
+        <v>1321</v>
       </c>
       <c r="D45" t="n">
-        <v>2.44</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>787.5</v>
+        <v>221.85</v>
       </c>
       <c r="C46" t="n">
-        <v>271.55</v>
+        <v>221.59</v>
       </c>
       <c r="D46" t="n">
-        <v>-65.52</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1270</v>
+        <v>12331</v>
       </c>
       <c r="C47" t="n">
-        <v>1223.1</v>
+        <v>12622</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.69</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1039</v>
+        <v>1576.8</v>
       </c>
       <c r="C48" t="n">
-        <v>1038</v>
+        <v>1507.8</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>464.85</v>
+        <v>352.41</v>
       </c>
       <c r="C49" t="n">
-        <v>448.4</v>
+        <v>404.35</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.54</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>284.05</v>
+        <v>612</v>
       </c>
       <c r="C50" t="n">
-        <v>299.55</v>
+        <v>607.75</v>
       </c>
       <c r="D50" t="n">
-        <v>5.46</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>212.12</v>
+        <v>212.72</v>
       </c>
       <c r="C51" t="n">
-        <v>211.36</v>
+        <v>211.2</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>393.6</v>
+        <v>7230</v>
       </c>
       <c r="C52" t="n">
-        <v>399.15</v>
+        <v>6427</v>
       </c>
       <c r="D52" t="n">
-        <v>1.41</v>
+        <v>-11.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>318.1</v>
+        <v>1881.6</v>
       </c>
       <c r="C53" t="n">
-        <v>318.35</v>
+        <v>1928</v>
       </c>
       <c r="D53" t="n">
-        <v>0.08</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>774.8</v>
+        <v>3640.5</v>
       </c>
       <c r="C54" t="n">
-        <v>813.35</v>
+        <v>4026.7</v>
       </c>
       <c r="D54" t="n">
-        <v>4.98</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4525.9</v>
+        <v>1736</v>
       </c>
       <c r="C55" t="n">
-        <v>4385.2</v>
+        <v>1475.4</v>
       </c>
       <c r="D55" t="n">
-        <v>-3.11</v>
+        <v>-15.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4628.5</v>
+        <v>1764.4</v>
       </c>
       <c r="C56" t="n">
-        <v>4585.9</v>
+        <v>1745.7</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.92</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4179.5</v>
+        <v>5266.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4185.1</v>
+        <v>5402</v>
       </c>
       <c r="D57" t="n">
-        <v>0.13</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1080.25</v>
+        <v>507.5</v>
       </c>
       <c r="C58" t="n">
-        <v>1068.45</v>
+        <v>468.35</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.09</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>462.75</v>
+        <v>607.75</v>
       </c>
       <c r="C59" t="n">
-        <v>431.3</v>
+        <v>603.1</v>
       </c>
       <c r="D59" t="n">
-        <v>-6.8</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>427.6</v>
+        <v>958.95</v>
       </c>
       <c r="C60" t="n">
-        <v>444.55</v>
+        <v>1029.5</v>
       </c>
       <c r="D60" t="n">
-        <v>3.96</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1359.1</v>
+        <v>1095.75</v>
       </c>
       <c r="C61" t="n">
-        <v>1268.3</v>
+        <v>1202.6</v>
       </c>
       <c r="D61" t="n">
-        <v>-6.68</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>438.75</v>
+        <v>699.7</v>
       </c>
       <c r="C62" t="n">
-        <v>481.45</v>
+        <v>744</v>
       </c>
       <c r="D62" t="n">
-        <v>9.73</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="64">
@@ -2875,523 +2819,347 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1657.3</v>
-      </c>
-      <c r="C67" t="n">
-        <v>5.33</v>
-      </c>
+        <v>2743.5</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9994</v>
+        <v>1519.1</v>
       </c>
       <c r="C68" t="n">
-        <v>2.26</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3278.8</v>
-      </c>
-      <c r="C69" t="n">
-        <v>8.58</v>
-      </c>
+        <v>1094.05</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1458.6</v>
+        <v>1063.65</v>
       </c>
       <c r="C70" t="n">
-        <v>13.46</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1808.3</v>
-      </c>
-      <c r="C71" t="inlineStr"/>
+        <v>781.35</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4) Leaving top portfolio — names that dropped out of top vs previous baseline</t>
-        </is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1326.1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>20.57</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3400.2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>14.43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Adj_Close</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Pct_vs_baseline</t>
-        </is>
-      </c>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1062.4</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1268.3</v>
+        <v>1290.8</v>
       </c>
       <c r="C76" t="n">
-        <v>-6.68</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>431.3</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-6.8</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>4585.9</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1068.45</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.09</v>
+          <t>4) Leaving top portfolio — names that dropped out of top vs previous baseline</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>271.55</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-65.52</v>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Adj_Close</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pct_vs_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>468.35</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-7.71</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5) Each previous baseline name — baseline vs current adj. close, rank at 2026-05-01 (exit monitor)</t>
-        </is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>6427</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-11.11</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>221.59</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Baseline_Adj_Close</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Current_Adj_Close</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Pct_vs_baseline</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Current_Rank</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>In_top_portfolio</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Within_exit_rank_band</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>12622</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>198.5</v>
+        <v>211.2</v>
       </c>
       <c r="C85" t="n">
-        <v>221.85</v>
-      </c>
-      <c r="D85" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>-0.71</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7000.87</v>
+        <v>404.35</v>
       </c>
       <c r="C86" t="n">
-        <v>7230</v>
-      </c>
-      <c r="D86" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E86" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>14.74</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5140.9</v>
+        <v>1507.8</v>
       </c>
       <c r="C87" t="n">
-        <v>5266.4</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E87" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>-4.38</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>787.5</v>
+        <v>603.1</v>
       </c>
       <c r="C88" t="n">
-        <v>271.55</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-65.52</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Failed screen — not in ranked universe this run</t>
-        </is>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1270</v>
+        <v>1029.5</v>
       </c>
       <c r="C89" t="n">
-        <v>1223.1</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-3.69</v>
-      </c>
-      <c r="E89" t="n">
-        <v>17</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>7.36</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1039</v>
+        <v>1475.4</v>
       </c>
       <c r="C90" t="n">
-        <v>1038</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>15</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>464.85</v>
-      </c>
-      <c r="C91" t="n">
-        <v>448.4</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-3.54</v>
-      </c>
-      <c r="E91" t="n">
-        <v>10</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>-15.01</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>284.05</v>
-      </c>
-      <c r="C92" t="n">
-        <v>299.55</v>
-      </c>
-      <c r="D92" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E92" t="n">
-        <v>4</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>212.12</v>
-      </c>
-      <c r="C93" t="n">
-        <v>211.36</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="E93" t="n">
-        <v>16</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>5) Each previous baseline name — baseline vs current adj. close, rank at 2026-05-15 (exit monitor)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>393.6</v>
-      </c>
-      <c r="C94" t="n">
-        <v>399.15</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E94" t="n">
-        <v>6</v>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Baseline_Adj_Close</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Current_Adj_Close</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pct_vs_baseline</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Current_Rank</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>In_top_portfolio</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Within_exit_rank_band</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>318.1</v>
+        <v>33550</v>
       </c>
       <c r="C95" t="n">
-        <v>318.35</v>
+        <v>32515</v>
       </c>
       <c r="D95" t="n">
-        <v>0.08</v>
+        <v>-3.08</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3408,20 +3176,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>774.8</v>
+        <v>4466.2</v>
       </c>
       <c r="C96" t="n">
-        <v>813.35</v>
+        <v>4333.7</v>
       </c>
       <c r="D96" t="n">
-        <v>4.98</v>
+        <v>-2.97</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3438,20 +3206,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4525.9</v>
+        <v>1266.75</v>
       </c>
       <c r="C97" t="n">
-        <v>4385.2</v>
+        <v>1321</v>
       </c>
       <c r="D97" t="n">
-        <v>-3.11</v>
+        <v>4.28</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3468,17 +3236,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>4628.5</v>
+        <v>221.85</v>
       </c>
       <c r="C98" t="n">
-        <v>4585.9</v>
+        <v>221.59</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.92</v>
+        <v>-0.12</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
@@ -3500,50 +3268,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>4179.5</v>
+        <v>12331</v>
       </c>
       <c r="C99" t="n">
-        <v>4185.1</v>
+        <v>12622</v>
       </c>
       <c r="D99" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E99" t="n">
-        <v>18</v>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Failed screen — not in ranked universe this run</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1080.25</v>
+        <v>1576.8</v>
       </c>
       <c r="C100" t="n">
-        <v>1068.45</v>
+        <v>1507.8</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.09</v>
+        <v>-4.38</v>
       </c>
       <c r="E100" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3557,28 +3327,26 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Below top 20 (universe rank 22)</t>
+          <t>Below top 20 (universe rank 24)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>462.75</v>
+        <v>352.41</v>
       </c>
       <c r="C101" t="n">
-        <v>431.3</v>
+        <v>404.35</v>
       </c>
       <c r="D101" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="E101" t="n">
-        <v>28</v>
-      </c>
+        <v>14.74</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>N</t>
@@ -3586,32 +3354,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Below top 20 (universe rank 28)</t>
+          <t>Failed screen — not in ranked universe this run</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>427.6</v>
+        <v>612</v>
       </c>
       <c r="C102" t="n">
-        <v>444.55</v>
+        <v>607.75</v>
       </c>
       <c r="D102" t="n">
-        <v>3.96</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E102" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3628,21 +3396,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1359.1</v>
+        <v>212.72</v>
       </c>
       <c r="C103" t="n">
-        <v>1268.3</v>
+        <v>211.2</v>
       </c>
       <c r="D103" t="n">
-        <v>-6.68</v>
-      </c>
-      <c r="E103" t="n">
-        <v>27</v>
-      </c>
+        <v>-0.71</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>N</t>
@@ -3650,44 +3416,358 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Below top 20 (universe rank 27)</t>
+          <t>Failed screen — not in ranked universe this run</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>438.75</v>
+        <v>7230</v>
       </c>
       <c r="C104" t="n">
-        <v>481.45</v>
+        <v>6427</v>
       </c>
       <c r="D104" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="E104" t="n">
-        <v>7</v>
-      </c>
+        <v>-11.11</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Failed screen — not in ranked universe this run</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1881.6</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E105" t="n">
+        <v>16</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3640.5</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4026.7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1736</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1475.4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-15.01</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Failed screen — not in ranked universe this run</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1764.4</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1745.7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="E108" t="n">
+        <v>11</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5266.4</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5402</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E109" t="n">
+        <v>15</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>507.5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>468.35</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="E110" t="n">
+        <v>86</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Below top 20 (universe rank 86)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>607.75</v>
+      </c>
+      <c r="C111" t="n">
+        <v>603.1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Failed screen — not in ranked universe this run</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>958.95</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1029.5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E112" t="n">
+        <v>28</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Below top 20 (universe rank 28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1095.75</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="E113" t="n">
+        <v>8</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>699.7</v>
+      </c>
+      <c r="C114" t="n">
+        <v>744</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="E114" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
